--- a/content/xls/NSO_f_regions_01.07.2025.xlsx
+++ b/content/xls/NSO_f_regions_01.07.2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\Новое\13.08\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CBB086-E75C-4C4A-8534-EADDAA075404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{624B01F5-E86A-4468-9DAA-11C50696F0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
